--- a/GWD Data/Motor Starter PRICE.xlsx
+++ b/GWD Data/Motor Starter PRICE.xlsx
@@ -849,7 +849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB0E4B6-B416-49AC-93E7-762D8FB4B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF97ABB-ABD8-4C61-8E00-9F064162B9A6}">
   <dimension ref="A1:G279"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Motor Starter PRICE.xlsx
+++ b/GWD Data/Motor Starter PRICE.xlsx
@@ -849,7 +849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF97ABB-ABD8-4C61-8E00-9F064162B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCF459F-1331-4060-843F-D1A347B4B9A6}">
   <dimension ref="A1:G279"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
